--- a/artfynd/S 2913-2024 artfynd.xlsx
+++ b/artfynd/S 2913-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778157</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044638</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044628</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044632</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778165</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778168</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778171</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778172</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044626</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044633</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044635</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044639</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046341</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046344</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046360</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046361</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046362</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046363</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2547,6 +2642,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123709334</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2676,6 +2776,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347888</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2783,6 +2888,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119579663</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2880,6 +2990,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044641</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2977,6 +3092,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046370</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3074,6 +3194,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046371</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3171,6 +3296,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778143</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3268,6 +3398,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778145</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3365,6 +3500,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778148</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3462,6 +3602,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778149</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3559,6 +3704,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778150</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3656,6 +3806,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778151</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3753,6 +3908,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778166</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3850,6 +4010,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044624</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3947,6 +4112,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044636</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4044,6 +4214,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046319</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4141,6 +4316,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046320</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4238,6 +4418,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046342</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4335,6 +4520,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046343</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4432,6 +4622,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046373</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4529,6 +4724,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778160</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4626,6 +4826,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778161</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4723,6 +4928,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778164</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4820,6 +5030,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044625</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4917,6 +5132,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044637</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5014,6 +5234,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046336</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5111,6 +5336,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778189</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5221,6 +5451,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123689929</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5318,6 +5553,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044629</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5415,6 +5655,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046322</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5512,6 +5757,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046313</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5609,6 +5859,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044623</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5706,6 +5961,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778175</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5803,6 +6063,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046364</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5915,6 +6180,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119579678</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6012,6 +6282,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778178</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6118,6 +6393,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044640</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6215,6 +6495,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044630</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6312,6 +6597,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044646</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6418,8 +6708,73 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120044645</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>